--- a/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T09:15:07+00:00</t>
+    <t>2023-06-13T09:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T09:23:37+00:00</t>
+    <t>2023-06-13T09:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T09:35:33+00:00</t>
+    <t>2023-06-13T09:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T09:42:48+00:00</t>
+    <t>2023-07-03T07:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-03T07:58:25+00:00</t>
+    <t>2023-07-18T09:37:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
